--- a/python3/docs/llm/pytorch/shops.xlsx
+++ b/python3/docs/llm/pytorch/shops.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jmlee/github/sample/python3/docs/llm/pytorch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFCFAB2-5CA8-F247-AE93-EACFAF7BD926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951D2D8A-B15B-574B-B4FC-1B8ECFBF3972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="28300" windowHeight="15800" xr2:uid="{720372AC-B578-ED4F-B4E6-D10E203B0B9F}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="28300" windowHeight="15780" xr2:uid="{720372AC-B578-ED4F-B4E6-D10E203B0B9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,43 +35,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>경복궁초등학교CU편의점</t>
-  </si>
-  <si>
-    <t>편의점</t>
-  </si>
-  <si>
-    <t>강남이디야커피</t>
+    <t>category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)교원구몬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학습지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도미노피자</t>
+  </si>
+  <si>
+    <t>식비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롯데마트청량리점</t>
+  </si>
+  <si>
+    <t>마트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시가올</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울에너지직영주유소</t>
+  </si>
+  <si>
+    <t>주유비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴포즈커피답십리초점</t>
   </si>
   <si>
     <t>카페</t>
-  </si>
-  <si>
-    <t>파리바게뜨강남역</t>
-  </si>
-  <si>
-    <t>제과점</t>
-  </si>
-  <si>
-    <t>교촌치킨신촌점</t>
-  </si>
-  <si>
-    <t>음식점</t>
-  </si>
-  <si>
-    <t>한성중학교</t>
-  </si>
-  <si>
-    <t>학교</t>
-  </si>
-  <si>
-    <t>category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴포즈커피자양동점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -79,7 +93,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -94,6 +108,18 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val=".SF NS"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -118,8 +144,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -436,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5EAC0DB-89BF-8E41-BA56-E5169AB1005E}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -448,47 +480,63 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>5</v>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="19">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
